--- a/output/Data and Chart Outputs/china_nbs_ppi_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_ppi_monthly.xlsx
@@ -22,9 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,6 +164,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -429,11 +430,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -461,14 +474,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -499,6 +520,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -692,11 +714,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -724,14 +758,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -762,6 +804,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -955,11 +998,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -987,14 +1042,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1025,6 +1088,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -1290,11 +1354,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -1322,14 +1398,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1767,6 +1851,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1781,6 +1866,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1855,7 +1941,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1881,7 +1967,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1907,7 +1993,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1933,7 +2019,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1959,7 +2045,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1985,7 +2071,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -2011,7 +2097,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -2037,7 +2123,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2063,7 +2149,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2089,7 +2175,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2115,7 +2201,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2141,7 +2227,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2167,7 +2253,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2193,7 +2279,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2219,7 +2305,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2245,7 +2331,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2271,7 +2357,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2297,7 +2383,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2323,7 +2409,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2349,7 +2435,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2375,7 +2461,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2401,7 +2487,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2427,7 +2513,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2453,7 +2539,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2479,7 +2565,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2505,7 +2591,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2531,7 +2617,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2557,7 +2643,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2583,7 +2669,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2609,7 +2695,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2635,7 +2721,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2661,7 +2747,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2687,7 +2773,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2713,7 +2799,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2739,7 +2825,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2765,7 +2851,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2791,7 +2877,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2817,7 +2903,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2843,7 +2929,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2869,7 +2955,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2895,7 +2981,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2921,7 +3007,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2947,7 +3033,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2973,7 +3059,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2999,7 +3085,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -3025,7 +3111,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3051,7 +3137,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3077,7 +3163,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3103,7 +3189,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3129,7 +3215,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3155,7 +3241,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3181,7 +3267,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3207,7 +3293,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3233,7 +3319,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3259,7 +3345,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3285,7 +3371,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3311,7 +3397,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3337,7 +3423,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3363,7 +3449,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3389,7 +3475,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3415,7 +3501,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -3441,7 +3527,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3467,7 +3553,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -3493,7 +3579,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -3519,7 +3605,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3545,7 +3631,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3571,7 +3657,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3597,7 +3683,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -3673,7 +3759,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -3693,7 +3779,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -3713,7 +3799,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -3733,7 +3819,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -3753,7 +3839,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3773,7 +3859,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3793,7 +3879,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3813,7 +3899,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3833,7 +3919,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3853,7 +3939,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3873,7 +3959,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3893,7 +3979,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3913,7 +3999,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3933,7 +4019,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3953,7 +4039,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3973,7 +4059,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3993,7 +4079,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -4013,7 +4099,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -4033,7 +4119,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -4053,7 +4139,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -4073,7 +4159,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -4093,7 +4179,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -4113,7 +4199,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -4133,7 +4219,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -4153,7 +4239,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -4173,7 +4259,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -4193,7 +4279,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -4213,7 +4299,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -4233,7 +4319,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -4253,7 +4339,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -4273,7 +4359,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -4293,7 +4379,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -4313,7 +4399,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -4333,7 +4419,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -4353,7 +4439,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -4373,7 +4459,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -4393,7 +4479,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -4413,7 +4499,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -4433,7 +4519,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -4453,7 +4539,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -4473,7 +4559,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -4493,7 +4579,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4513,7 +4599,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4533,7 +4619,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4553,7 +4639,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4573,7 +4659,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4593,7 +4679,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4613,7 +4699,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4633,7 +4719,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4653,7 +4739,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4673,7 +4759,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4693,7 +4779,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4713,7 +4799,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4733,7 +4819,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4753,7 +4839,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4773,7 +4859,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4793,7 +4879,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4813,7 +4899,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4833,7 +4919,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4853,7 +4939,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4873,7 +4959,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4893,7 +4979,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4913,7 +4999,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4933,7 +5019,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4953,7 +5039,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -4973,7 +5059,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -4993,7 +5079,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -5013,7 +5099,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -5083,7 +5169,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -5103,7 +5189,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -5123,7 +5209,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -5143,7 +5229,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -5163,7 +5249,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -5183,7 +5269,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -5203,7 +5289,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -5223,7 +5309,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -5243,7 +5329,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -5263,7 +5349,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -5283,7 +5369,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -5303,7 +5389,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -5323,7 +5409,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -5343,7 +5429,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -5363,7 +5449,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -5383,7 +5469,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -5403,7 +5489,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -5423,7 +5509,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -5443,7 +5529,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -5463,7 +5549,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -5483,7 +5569,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -5503,7 +5589,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -5523,7 +5609,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -5543,7 +5629,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -5563,7 +5649,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -5583,7 +5669,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -5603,7 +5689,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -5623,7 +5709,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -5643,7 +5729,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -5663,7 +5749,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -5683,7 +5769,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -5703,7 +5789,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -5723,7 +5809,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -5743,7 +5829,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -5763,7 +5849,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -5783,7 +5869,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -5803,7 +5889,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -5823,7 +5909,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -5843,7 +5929,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -5863,7 +5949,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -5883,7 +5969,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -5903,7 +5989,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -5923,7 +6009,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -5943,7 +6029,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -5963,7 +6049,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -5983,7 +6069,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -6003,7 +6089,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -6023,7 +6109,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -6043,7 +6129,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -6063,7 +6149,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -6083,7 +6169,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -6103,7 +6189,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -6123,7 +6209,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -6143,7 +6229,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -6163,7 +6249,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -6183,7 +6269,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -6203,7 +6289,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -6223,7 +6309,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -6243,7 +6329,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -6263,7 +6349,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -6283,7 +6369,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -6303,7 +6389,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -6323,7 +6409,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -6343,7 +6429,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -6363,7 +6449,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -6383,7 +6469,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -6403,7 +6489,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -6423,7 +6509,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -6503,7 +6589,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -6529,7 +6615,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -6555,7 +6641,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -6581,7 +6667,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -6607,7 +6693,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -6633,7 +6719,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -6659,7 +6745,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -6685,7 +6771,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -6711,7 +6797,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -6737,7 +6823,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -6763,7 +6849,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -6789,7 +6875,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -6815,7 +6901,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -6841,7 +6927,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -6867,7 +6953,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -6893,7 +6979,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -6919,7 +7005,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -6945,7 +7031,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -6971,7 +7057,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -6997,7 +7083,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -7023,7 +7109,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -7049,7 +7135,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -7075,7 +7161,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -7101,7 +7187,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -7127,7 +7213,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -7153,7 +7239,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -7179,7 +7265,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -7205,7 +7291,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -7231,7 +7317,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -7257,7 +7343,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -7283,7 +7369,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -7309,7 +7395,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -7335,7 +7421,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -7361,7 +7447,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -7387,7 +7473,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -7413,7 +7499,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -7439,7 +7525,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -7465,7 +7551,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -7491,7 +7577,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -7517,7 +7603,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -7543,7 +7629,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -7569,7 +7655,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -7595,7 +7681,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -7621,7 +7707,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -7647,7 +7733,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -7673,7 +7759,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -7699,7 +7785,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -7725,7 +7811,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -7751,7 +7837,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -7777,7 +7863,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -7803,7 +7889,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -7829,7 +7915,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -7855,7 +7941,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -7881,7 +7967,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -7907,7 +7993,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -7933,7 +8019,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -7959,7 +8045,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -7985,7 +8071,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -8011,7 +8097,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -8037,7 +8123,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -8063,7 +8149,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -8089,7 +8175,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -8115,7 +8201,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -8141,7 +8227,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -8167,7 +8253,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -8193,7 +8279,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -8219,7 +8305,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -8245,7 +8331,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">

--- a/output/Data and Chart Outputs/china_nbs_ppi_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_ppi_monthly.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China PPI headline y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China PPI headline y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$165</f>
+              <f>'Chart'!$B$2:$B$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -232,12 +232,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$165</f>
+              <f>'Chart'!$C$2:$C$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -268,12 +268,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$165</f>
+              <f>'Chart'!$D$2:$D$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -304,12 +304,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$165</f>
+              <f>'Chart'!$E$2:$E$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -340,12 +340,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$165</f>
+              <f>'Chart'!$F$2:$F$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -376,12 +376,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$165</f>
+              <f>'Chart'!$G$2:$G$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -412,12 +412,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$165</f>
+              <f>'Chart'!$H$2:$H$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -517,7 +517,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China PPI purchaser prices y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China PPI purchaser prices y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$B$2:$B$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$B$2:$B$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -589,12 +589,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$C$2:$C$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$C$2:$C$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -625,12 +625,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$D$2:$D$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$D$2:$D$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -661,12 +661,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$E$2:$E$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$E$2:$E$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -697,12 +697,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI purchaser prices y-'!$F$2:$F$165</f>
+              <f>'Chart - PPI purchaser prices y-'!$F$2:$F$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -802,7 +802,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China PPI energy industries y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China PPI energy industries y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -838,12 +838,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$A$2:$A$158</f>
+              <f>'Chart - PPI energy industries y'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$B$2:$B$158</f>
+              <f>'Chart - PPI energy industries y'!$B$2:$B$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$A$2:$A$158</f>
+              <f>'Chart - PPI energy industries y'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$C$2:$C$158</f>
+              <f>'Chart - PPI energy industries y'!$C$2:$C$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -910,12 +910,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$A$2:$A$158</f>
+              <f>'Chart - PPI energy industries y'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$D$2:$D$158</f>
+              <f>'Chart - PPI energy industries y'!$D$2:$D$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -946,12 +946,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$A$2:$A$158</f>
+              <f>'Chart - PPI energy industries y'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$E$2:$E$158</f>
+              <f>'Chart - PPI energy industries y'!$E$2:$E$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -982,12 +982,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$A$2:$A$158</f>
+              <f>'Chart - PPI energy industries y'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI energy industries y'!$F$2:$F$158</f>
+              <f>'Chart - PPI energy industries y'!$F$2:$F$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1087,7 +1087,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China PPI metals and materials y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China PPI metals and materials y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1123,12 +1123,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$B$2:$B$158</f>
+              <f>'Chart - PPI metals and material'!$B$2:$B$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1159,12 +1159,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$C$2:$C$158</f>
+              <f>'Chart - PPI metals and material'!$C$2:$C$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1195,12 +1195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$D$2:$D$158</f>
+              <f>'Chart - PPI metals and material'!$D$2:$D$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1231,12 +1231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$E$2:$E$158</f>
+              <f>'Chart - PPI metals and material'!$E$2:$E$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$F$2:$F$158</f>
+              <f>'Chart - PPI metals and material'!$F$2:$F$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1303,12 +1303,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$G$2:$G$158</f>
+              <f>'Chart - PPI metals and material'!$G$2:$G$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1339,12 +1339,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - PPI metals and material'!$A$2:$A$158</f>
+              <f>'Chart - PPI metals and material'!$A$2:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - PPI metals and material'!$H$2:$H$158</f>
+              <f>'Chart - PPI metals and material'!$H$2:$H$159</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1896,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6206,6 +6206,32 @@
       </c>
       <c r="H165" t="n">
         <v>5.8</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D166" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E166" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F166" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -6220,7 +6246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9536,6 +9562,26 @@
       </c>
       <c r="F165" t="n">
         <v>-3.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D166" t="n">
+        <v>20</v>
+      </c>
+      <c r="E166" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-2.3</v>
       </c>
     </row>
   </sheetData>
@@ -9550,7 +9596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12564,6 +12610,26 @@
       </c>
       <c r="F158" t="n">
         <v>4.2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B159" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="C159" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D159" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="F159" t="n">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -12578,7 +12644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16706,6 +16772,32 @@
       </c>
       <c r="H158" t="n">
         <v>9.6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B159" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C159" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E159" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G159" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>
@@ -16720,7 +16812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU165"/>
+  <dimension ref="A1:EU166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77914,6 +78006,461 @@
       </c>
       <c r="EU165" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E166" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H166" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K166" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L166" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M166" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P166" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T166" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V166" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W166" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR166" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BS166" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="BT166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="BU166" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BV166" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BW166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BX166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BY166" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="BZ166" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB166" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="CC166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CD166" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="CE166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CF166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CG166" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CH166" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="CI166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CJ166" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="CK166" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="CL166" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CM166" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="CN166" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="CO166" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CP166" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="CQ166" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="CR166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CS166" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT166" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="CU166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CV166" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="CW166" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="CX166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CY166" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="CZ166" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="DA166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="DB166" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="DC166" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="DD166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DE166" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="DF166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DI166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DJ166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DK166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DL166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DM166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DN166" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="DO166" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="DP166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DQ166" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="DR166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DS166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="DT166" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="DU166" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="DV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW166" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="DX166" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="DY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ166" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="EA166" t="n">
+        <v>2</v>
+      </c>
+      <c r="EB166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="EC166" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="ED166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="EE166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="EF166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="EG166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="EH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI166" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="EJ166" t="n">
+        <v>-2</v>
+      </c>
+      <c r="EK166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="EL166" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="EM166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="EN166" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="EP166" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="EQ166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="ER166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="ES166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="ET166" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU166" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
